--- a/downloads/indicadores/IMAI/IMAI_datos.xlsx
+++ b/downloads/indicadores/IMAI/IMAI_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -577,14 +577,14 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>May 25 P</t>
+          <t>Ene 18</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45778</v>
+        <v>43101</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>101.579489</v>
+        <v>99.84084900000001</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -635,18 +635,18 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Jun 25 P</t>
+          <t>Feb 18</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>45809</v>
+        <v>43132</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>101.250003</v>
+        <v>100.271051</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -693,18 +693,18 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Jul 25 P</t>
+          <t>Mar 18</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>45839</v>
+        <v>43160</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>100.232315</v>
+        <v>100.322778</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -751,18 +751,18 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Ago 25 P</t>
+          <t>Abr 18</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>45870</v>
+        <v>43191</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>100.042784</v>
+        <v>98.990911</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -809,18 +809,18 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Sep 25 P</t>
+          <t>May 18</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>45901</v>
+        <v>43221</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>99.896912</v>
+        <v>100.66695</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -867,18 +867,18 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Oct 25 P</t>
+          <t>Jun 18</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>45931</v>
+        <v>43252</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>100.714133</v>
+        <v>100.49004</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -925,18 +925,18 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Nov 25 P</t>
+          <t>Jul 18</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45962</v>
+        <v>43282</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>101.317257</v>
+        <v>100.810098</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -983,18 +983,18 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Dic 25 P</t>
+          <t>Ago 18</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45992</v>
+        <v>43313</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>101.430223</v>
+        <v>99.980861</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1041,18 +1041,18 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Ene 26 P</t>
+          <t>Sep 18</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>46023</v>
+        <v>43344</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>100.399604</v>
+        <v>101.074552</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>+1.1%</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1099,18 +1099,18 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Feb 26 P</t>
+          <t>Oct 18</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>46054</v>
+        <v>43374</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>100.824971</v>
+        <v>100.169133</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -1157,18 +1157,18 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Nov 18</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>46082</v>
+        <v>43405</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>100.297622</v>
+        <v>99.182526</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1215,18 +1215,18 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Abr 26 P</t>
+          <t>Dic 18</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>46113</v>
+        <v>43435</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>102.419928</v>
+        <v>98.922071</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1273,56 +1273,5160 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Ene 19</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>99.076626</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Feb 19</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n">
+        <v>43497</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>99.561381</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Mar 19</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>43525</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>98.337873</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Abr 19</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>99.340782</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>May 19</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>43586</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>98.426799</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Jun 19</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>43617</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>99.397645</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Jul 19</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>98.806605</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Ago 19</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>43678</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>98.634236</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Sep 19</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>43709</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>98.555543</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>-2.5%</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Oct 19</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>96.51451</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>-3.6%</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Nov 19</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>43770</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>96.922496</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>-2.3%</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Dic 19</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>43800</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>96.15925300000001</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Ene 20</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>97.320674</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>-1.8%</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Feb 20</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>43862</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>96.75405000000001</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Mar 20</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>43891</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>93.560802</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>-4.9%</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Abr 20</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>69.864321</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>-29.7%</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43952</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>69.771418</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>-29.1%</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Jun 20</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>43983</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>84.88603000000001</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>-14.6%</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>88.62421500000001</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>-10.3%</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Ago 20</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>44044</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>91.982553</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>-6.7%</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sep 20</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>44075</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>94.268389</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>-4.3%</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Oct 20</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>95.493455</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Nov 20</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>44136</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>95.868044</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>-1.1%</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Dic 20</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>44166</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>95.407017</v>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Ene 21</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>94.659227</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>-2.7%</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Feb 21</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>44228</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>93.65984</v>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>-3.2%</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Mar 21</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>44256</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>95.786074</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>+2.4%</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Abr 21</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>95.609086</v>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>+36.8%</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>44317</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>95.093763</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>+36.3%</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>44348</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>94.92609899999999</v>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>+11.8%</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Jul 21</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>95.13120000000001</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>+7.3%</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Ago 21</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>44409</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>95.482185</v>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>+3.8%</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sep 21</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>44440</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>94.462007</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>+0.2%</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Oct 21</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>95.46743600000001</v>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Nov 21</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>44501</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>95.969927</v>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Dic 21</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="n">
+        <v>44531</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>97.184878</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>+1.9%</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Ene 22</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>98.407748</v>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Feb 22</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>44593</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>98.36582199999999</v>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>44621</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>99.291353</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>+3.7%</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Abr 22</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>99.881023</v>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>+4.5%</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>44682</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>99.684168</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>+4.8%</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>44713</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>99.147328</v>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>+4.4%</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Jul 22</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>99.824502</v>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>+4.9%</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Ago 22</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>44774</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>100.255836</v>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Sep 22</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>44805</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>99.839226</v>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>+5.7%</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Oct 22</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>99.86564199999999</v>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>+4.6%</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Nov 22</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>44866</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>100.962623</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>+5.2%</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Dic 22</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>44896</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>102.383417</v>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>+5.3%</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Ene 23</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>101.928352</v>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>+3.6%</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Feb 23</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>44958</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>101.614738</v>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>+3.3%</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>44986</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>101.624389</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>+2.3%</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Abr 23</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>102.113348</v>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>+2.2%</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>45047</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>102.603925</v>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>+2.9%</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>45078</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>103.032062</v>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>+3.9%</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Jul 23</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>102.993711</v>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>+3.2%</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Ago 23</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>45139</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>103.14479</v>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>+2.9%</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Sep 23</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>45170</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>103.813038</v>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Oct 23</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>104.817918</v>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Nov 23</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>45231</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>103.107057</v>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>+2.1%</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Dic 23</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>103.036966</v>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Ene 24</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>103.634152</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>+1.7%</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Feb 24</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>45323</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>102.030078</v>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Mar 24</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>45352</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>102.633837</v>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>+1.0%</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Abr 24</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>101.627113</v>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>May 24</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>45413</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>101.822934</v>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>45444</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>102.090292</v>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Jul 24</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>102.762047</v>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Ago 24</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n">
+        <v>45505</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>102.256141</v>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Sep 24</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>45536</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>102.885165</v>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>Oct 24</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>101.141931</v>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>-3.5%</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>45597</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>101.328175</v>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>-1.7%</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
+        <v>45627</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>100.100472</v>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Ene 25</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>100.345389</v>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>-3.2%</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
+        <v>45689</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>102.121506</v>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>45717</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>101.691373</v>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>100.610819</v>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>-1.0%</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>May 25 P</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>45778</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>101.579489</v>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Jun 25 P</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="n">
+        <v>45809</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>101.250003</v>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Jul 25 P</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>100.232315</v>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>-2.5%</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Ago 25 P</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="n">
+        <v>45870</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>100.042784</v>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Sep 25 P</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>99.896912</v>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>-2.9%</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>Oct 25 P</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>100.714133</v>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Nov 25 P</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>45962</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>101.317257</v>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>Dic 25 P</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>101.430223</v>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>+1.3%</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Ene 26 P</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>46023</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>100.399604</v>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>Feb 26 P</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n">
+        <v>46054</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>100.824971</v>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>-1.3%</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L103" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Mar 26 P</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>46082</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>100.297622</v>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>Abr 26 P</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>102.419928</v>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>+1.8%</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>Preliminar</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B106" s="5" t="n">
         <v>46143</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C106" s="6" t="n">
         <v>101.629971</v>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D106" s="4" t="inlineStr">
         <is>
           <t>+0.0%</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Índice base 2018=100</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Serie original</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Definitivo</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
         <is>
           <t>10 de julio de 2026</t>
         </is>

--- a/downloads/indicadores/IMAI/IMAI_datos.xlsx
+++ b/downloads/indicadores/IMAI/IMAI_datos.xlsx
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234 · Fecha de publicación: 10 de julio de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234 · Fecha de publicación: 11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>10 de julio de 2026</t>
+          <t>11 de agosto de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/IMAI/IMAI_datos.xlsx
+++ b/downloads/indicadores/IMAI/IMAI_datos.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234 · Fecha de publicación: 11 de agosto de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf · Fecha de publicación: 11 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -6423,10 +6423,68 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>11 de agosto de 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="n">
+        <v>46174</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>Definitivo</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imai/imai2026_08.pdf</t>
+        </is>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
         <is>
           <t>11 de agosto de 2026</t>
         </is>

--- a/downloads/indicadores/IMAI/IMAI_datos.xlsx
+++ b/downloads/indicadores/IMAI/IMAI_datos.xlsx
@@ -5681,7 +5681,7 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>May 25 P</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B94" s="5" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5739,7 +5739,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Jun 25 P</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B95" s="8" t="n">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Jul 25 P</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B96" s="5" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
@@ -5855,7 +5855,7 @@
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Ago 25 P</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B97" s="8" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Sep 25 P</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B98" s="5" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -5971,7 +5971,7 @@
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Oct 25 P</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B99" s="8" t="n">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
@@ -6029,7 +6029,7 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Nov 25 P</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B100" s="5" t="n">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J100" s="4" t="inlineStr">
@@ -6087,7 +6087,7 @@
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Dic 25 P</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B101" s="8" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
@@ -6145,7 +6145,7 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Ene 26 P</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B102" s="5" t="n">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J102" s="4" t="inlineStr">
@@ -6203,7 +6203,7 @@
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Feb 26 P</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B103" s="8" t="n">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
@@ -6261,7 +6261,7 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Mar 26</t>
         </is>
       </c>
       <c r="B104" s="5" t="n">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="I104" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J104" s="4" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Abr 26 P</t>
+          <t>Abr 26</t>
         </is>
       </c>
       <c r="B105" s="8" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">

--- a/downloads/indicadores/IMAI/IMAI_datos.xlsx
+++ b/downloads/indicadores/IMAI/IMAI_datos.xlsx
@@ -10108,7 +10108,7 @@
         <v>45597</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>101.323968</v>
+        <v>103.3</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>90.242272</v>
@@ -10133,7 +10133,7 @@
         <v>45627</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>100.10177</v>
+        <v>101.4</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>89.34519</v>
@@ -10158,7 +10158,7 @@
         <v>45658</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>100.329934</v>
+        <v>100.8</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>87.840372</v>
@@ -10183,7 +10183,7 @@
         <v>45689</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>102.088963</v>
+        <v>103.2</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>88.23526</v>
@@ -10208,7 +10208,7 @@
         <v>45717</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>101.695397</v>
+        <v>102.5</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>85.86011499999999</v>
@@ -10233,7 +10233,7 @@
         <v>45748</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>100.654217</v>
+        <v>102.5</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>87.348224</v>
@@ -10258,7 +10258,7 @@
         <v>45778</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>101.606909</v>
+        <v>103.3</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>86.6478</v>
@@ -10283,7 +10283,7 @@
         <v>45809</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>101.201605</v>
+        <v>103.2</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>85.322898</v>
@@ -10308,7 +10308,7 @@
         <v>45839</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>100.238256</v>
+        <v>101.6</v>
       </c>
       <c r="D396" s="6" t="n">
         <v>87.70510299999999</v>
@@ -10333,7 +10333,7 @@
         <v>45870</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>100.052653</v>
+        <v>101.1</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>87.990143</v>
@@ -10358,7 +10358,7 @@
         <v>45901</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>99.90134500000001</v>
+        <v>99.5</v>
       </c>
       <c r="D398" s="6" t="n">
         <v>88.643006</v>
@@ -10383,7 +10383,7 @@
         <v>45931</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>100.715175</v>
+        <v>100.5</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>89.280682</v>
@@ -10408,7 +10408,7 @@
         <v>45962</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>101.314732</v>
+        <v>101.4</v>
       </c>
       <c r="D400" s="6" t="n">
         <v>89.27523100000001</v>
@@ -10433,7 +10433,7 @@
         <v>45992</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>101.432921</v>
+        <v>101.7</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>89.72416699999999</v>
@@ -10458,7 +10458,7 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>100.466565</v>
+        <v>100.3</v>
       </c>
       <c r="D402" s="6" t="n">
         <v>88.76888</v>
@@ -10483,7 +10483,7 @@
         <v>46054</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>100.964971</v>
+        <v>100.7</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>89.98042100000001</v>
@@ -10508,7 +10508,7 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>100.402353</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D404" s="6" t="n">
         <v>90.551627</v>
@@ -10533,7 +10533,7 @@
         <v>46113</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>102.497387</v>
+        <v>102.4</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>90.388932</v>
@@ -10558,7 +10558,7 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>101.768601</v>
+        <v>101.6</v>
       </c>
       <c r="D406" s="6" t="n">
         <v>90.69598499999999</v>
@@ -10583,7 +10583,7 @@
         <v>46174</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>101.992466</v>
+        <v>102</v>
       </c>
       <c r="D407" s="7" t="n">
         <v>91.26119300000001</v>
@@ -20004,34 +20004,34 @@
         <v>45597</v>
       </c>
       <c r="C388" s="9" t="n">
-        <v>0.001801</v>
+        <v>0.001</v>
       </c>
       <c r="D388" s="9" t="n">
-        <v>-0.017317</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="E388" s="9" t="n">
-        <v>0.003835</v>
+        <v>0.004</v>
       </c>
       <c r="F388" s="9" t="n">
-        <v>0.005466</v>
+        <v>0.008</v>
       </c>
       <c r="G388" s="9" t="n">
-        <v>0.002376</v>
+        <v>-0.018</v>
       </c>
       <c r="H388" s="9" t="n">
-        <v>0.00045</v>
+        <v>0.007</v>
       </c>
       <c r="I388" s="9" t="n">
-        <v>-0.075626</v>
+        <v>-0.045</v>
       </c>
       <c r="J388" s="9" t="n">
-        <v>-0.015477</v>
+        <v>0.029</v>
       </c>
       <c r="K388" s="9" t="n">
-        <v>-0.042407</v>
+        <v>-0.044</v>
       </c>
       <c r="L388" s="9" t="n">
-        <v>-0.000431</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="389">
@@ -20044,34 +20044,34 @@
         <v>45627</v>
       </c>
       <c r="C389" s="10" t="n">
-        <v>-0.012062</v>
+        <v>-0.014</v>
       </c>
       <c r="D389" s="10" t="n">
-        <v>-0.028504</v>
+        <v>-0.024</v>
       </c>
       <c r="E389" s="10" t="n">
-        <v>-0.009941</v>
+        <v>-0.01</v>
       </c>
       <c r="F389" s="10" t="n">
-        <v>-0.023042</v>
+        <v>-0.019</v>
       </c>
       <c r="G389" s="10" t="n">
-        <v>-0.019843</v>
+        <v>-0.021</v>
       </c>
       <c r="H389" s="10" t="n">
-        <v>-0.008756</v>
+        <v>-0.012</v>
       </c>
       <c r="I389" s="10" t="n">
-        <v>-0.087746</v>
+        <v>-0.062</v>
       </c>
       <c r="J389" s="10" t="n">
-        <v>-0.026871</v>
+        <v>0.018</v>
       </c>
       <c r="K389" s="10" t="n">
-        <v>-0.061743</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="L389" s="10" t="n">
-        <v>-0.005903</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="390">
@@ -20084,34 +20084,34 @@
         <v>45658</v>
       </c>
       <c r="C390" s="9" t="n">
-        <v>0.002279</v>
+        <v>-0.004</v>
       </c>
       <c r="D390" s="9" t="n">
-        <v>-0.031809</v>
+        <v>-0.028</v>
       </c>
       <c r="E390" s="9" t="n">
-        <v>-0.016843</v>
+        <v>-0.018</v>
       </c>
       <c r="F390" s="9" t="n">
-        <v>0.012102</v>
+        <v>-0.008</v>
       </c>
       <c r="G390" s="9" t="n">
-        <v>0.002539</v>
+        <v>0.001</v>
       </c>
       <c r="H390" s="9" t="n">
-        <v>0.004062</v>
+        <v>-0.003</v>
       </c>
       <c r="I390" s="9" t="n">
-        <v>-0.117057</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="J390" s="9" t="n">
-        <v>0.021327</v>
+        <v>0.01</v>
       </c>
       <c r="K390" s="9" t="n">
-        <v>-0.080691</v>
+        <v>-0.064</v>
       </c>
       <c r="L390" s="9" t="n">
-        <v>-0.00448</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="391">
@@ -20124,34 +20124,34 @@
         <v>45689</v>
       </c>
       <c r="C391" s="10" t="n">
-        <v>0.017532</v>
+        <v>0.025</v>
       </c>
       <c r="D391" s="10" t="n">
-        <v>0.000743</v>
+        <v>0.004</v>
       </c>
       <c r="E391" s="10" t="n">
-        <v>0.004496</v>
+        <v>0.008</v>
       </c>
       <c r="F391" s="10" t="n">
-        <v>0.006847</v>
+        <v>-0.004</v>
       </c>
       <c r="G391" s="10" t="n">
-        <v>0.038584</v>
+        <v>0.028</v>
       </c>
       <c r="H391" s="10" t="n">
-        <v>0.014505</v>
+        <v>0.029</v>
       </c>
       <c r="I391" s="10" t="n">
-        <v>-0.102963</v>
+        <v>-0.063</v>
       </c>
       <c r="J391" s="10" t="n">
-        <v>0.003246</v>
+        <v>-0.011</v>
       </c>
       <c r="K391" s="10" t="n">
-        <v>0.002515</v>
+        <v>0.005</v>
       </c>
       <c r="L391" s="10" t="n">
-        <v>0.018217</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="392">
@@ -20164,34 +20164,34 @@
         <v>45717</v>
       </c>
       <c r="C392" s="9" t="n">
-        <v>-0.003855</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D392" s="9" t="n">
-        <v>-0.009154000000000001</v>
+        <v>-0.013</v>
       </c>
       <c r="E392" s="9" t="n">
-        <v>-0.026918</v>
+        <v>-0.027</v>
       </c>
       <c r="F392" s="9" t="n">
-        <v>-0.011159</v>
+        <v>-0.011</v>
       </c>
       <c r="G392" s="9" t="n">
-        <v>0.027171</v>
+        <v>0.008</v>
       </c>
       <c r="H392" s="9" t="n">
-        <v>-0.009159</v>
+        <v>-0.011</v>
       </c>
       <c r="I392" s="9" t="n">
-        <v>-0.106163</v>
+        <v>-0.101</v>
       </c>
       <c r="J392" s="9" t="n">
-        <v>-0.018411</v>
+        <v>-0.034</v>
       </c>
       <c r="K392" s="9" t="n">
-        <v>0.024595</v>
+        <v>0.021</v>
       </c>
       <c r="L392" s="9" t="n">
-        <v>-0.003725</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="393">
@@ -20204,34 +20204,34 @@
         <v>45748</v>
       </c>
       <c r="C393" s="10" t="n">
-        <v>-0.010238</v>
+        <v>0.001</v>
       </c>
       <c r="D393" s="10" t="n">
-        <v>-0.009716000000000001</v>
+        <v>-0.007</v>
       </c>
       <c r="E393" s="10" t="n">
-        <v>0.017332</v>
+        <v>0.013</v>
       </c>
       <c r="F393" s="10" t="n">
-        <v>0.00229</v>
+        <v>0.001</v>
       </c>
       <c r="G393" s="10" t="n">
-        <v>-0.060975</v>
+        <v>-0.02</v>
       </c>
       <c r="H393" s="10" t="n">
-        <v>0.00061</v>
+        <v>0.007</v>
       </c>
       <c r="I393" s="10" t="n">
-        <v>-0.07326199999999999</v>
+        <v>-0.068</v>
       </c>
       <c r="J393" s="10" t="n">
-        <v>0.012085</v>
+        <v>-0.001</v>
       </c>
       <c r="K393" s="10" t="n">
-        <v>-0.048826</v>
+        <v>-0.027</v>
       </c>
       <c r="L393" s="10" t="n">
-        <v>0.015752</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="394">
@@ -20244,34 +20244,34 @@
         <v>45778</v>
       </c>
       <c r="C394" s="9" t="n">
-        <v>0.009464999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="D394" s="9" t="n">
-        <v>-0.002243</v>
+        <v>-0.004</v>
       </c>
       <c r="E394" s="9" t="n">
-        <v>-0.008019</v>
+        <v>-0.011</v>
       </c>
       <c r="F394" s="9" t="n">
-        <v>0.002426</v>
+        <v>0.004</v>
       </c>
       <c r="G394" s="9" t="n">
-        <v>0.053515</v>
+        <v>0.028</v>
       </c>
       <c r="H394" s="9" t="n">
-        <v>0.000409</v>
+        <v>0.001</v>
       </c>
       <c r="I394" s="9" t="n">
-        <v>-0.08178299999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J394" s="9" t="n">
-        <v>-0.02676</v>
+        <v>-0.038</v>
       </c>
       <c r="K394" s="9" t="n">
-        <v>-0.009742000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="L394" s="9" t="n">
-        <v>0.015008</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="395">
@@ -20284,34 +20284,34 @@
         <v>45809</v>
       </c>
       <c r="C395" s="10" t="n">
-        <v>-0.003989</v>
+        <v>-0.001</v>
       </c>
       <c r="D395" s="10" t="n">
-        <v>-0.008612</v>
+        <v>-0.008</v>
       </c>
       <c r="E395" s="10" t="n">
-        <v>-0.015291</v>
+        <v>-0.014</v>
       </c>
       <c r="F395" s="10" t="n">
-        <v>-0.005253</v>
+        <v>-0.002</v>
       </c>
       <c r="G395" s="10" t="n">
-        <v>-0.01689</v>
+        <v>-0.002</v>
       </c>
       <c r="H395" s="10" t="n">
-        <v>0.001485</v>
+        <v>0.003</v>
       </c>
       <c r="I395" s="10" t="n">
-        <v>-0.082473</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J395" s="10" t="n">
-        <v>-0.028596</v>
+        <v>-0.038</v>
       </c>
       <c r="K395" s="10" t="n">
-        <v>0.004225</v>
+        <v>0.015</v>
       </c>
       <c r="L395" s="10" t="n">
-        <v>0.00055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -20324,34 +20324,34 @@
         <v>45839</v>
       </c>
       <c r="C396" s="9" t="n">
-        <v>-0.009519</v>
+        <v>-0.012</v>
       </c>
       <c r="D396" s="9" t="n">
-        <v>-0.024575</v>
+        <v>-0.028</v>
       </c>
       <c r="E396" s="9" t="n">
-        <v>0.02792</v>
+        <v>0.019</v>
       </c>
       <c r="F396" s="9" t="n">
-        <v>-0.000549</v>
+        <v>-0.001</v>
       </c>
       <c r="G396" s="9" t="n">
-        <v>-0.002394</v>
+        <v>-0.012</v>
       </c>
       <c r="H396" s="9" t="n">
-        <v>-0.015605</v>
+        <v>-0.016</v>
       </c>
       <c r="I396" s="9" t="n">
-        <v>-0.059472</v>
+        <v>-0.059</v>
       </c>
       <c r="J396" s="9" t="n">
-        <v>-0.026099</v>
+        <v>-0.037</v>
       </c>
       <c r="K396" s="9" t="n">
-        <v>-0.041751</v>
+        <v>-0.041</v>
       </c>
       <c r="L396" s="9" t="n">
-        <v>-0.013886</v>
+        <v>-0.018</v>
       </c>
     </row>
     <row r="397">
@@ -20364,34 +20364,34 @@
         <v>45870</v>
       </c>
       <c r="C397" s="10" t="n">
-        <v>-0.001852</v>
+        <v>-0.003</v>
       </c>
       <c r="D397" s="10" t="n">
-        <v>-0.021587</v>
+        <v>-0.027</v>
       </c>
       <c r="E397" s="10" t="n">
-        <v>0.00325</v>
+        <v>-0.007</v>
       </c>
       <c r="F397" s="10" t="n">
-        <v>0.009941</v>
+        <v>0.013</v>
       </c>
       <c r="G397" s="10" t="n">
-        <v>-0.018026</v>
+        <v>-0.022</v>
       </c>
       <c r="H397" s="10" t="n">
-        <v>0.000398</v>
+        <v>0.002</v>
       </c>
       <c r="I397" s="10" t="n">
-        <v>-0.062695</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J397" s="10" t="n">
-        <v>-0.015806</v>
+        <v>-0.024</v>
       </c>
       <c r="K397" s="10" t="n">
-        <v>-0.022674</v>
+        <v>-0.032</v>
       </c>
       <c r="L397" s="10" t="n">
-        <v>-0.014845</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="398">
@@ -20404,34 +20404,34 @@
         <v>45901</v>
       </c>
       <c r="C398" s="9" t="n">
-        <v>-0.001512</v>
+        <v>-0.004</v>
       </c>
       <c r="D398" s="9" t="n">
-        <v>-0.029057</v>
+        <v>-0.033</v>
       </c>
       <c r="E398" s="9" t="n">
-        <v>0.00742</v>
+        <v>0.007</v>
       </c>
       <c r="F398" s="9" t="n">
-        <v>0.003361</v>
+        <v>0.004</v>
       </c>
       <c r="G398" s="9" t="n">
-        <v>-0.020885</v>
+        <v>-0.025</v>
       </c>
       <c r="H398" s="9" t="n">
-        <v>0.002406</v>
+        <v>0.002</v>
       </c>
       <c r="I398" s="9" t="n">
-        <v>-0.032038</v>
+        <v>-0.032</v>
       </c>
       <c r="J398" s="9" t="n">
-        <v>-0.001671</v>
+        <v>-0.002</v>
       </c>
       <c r="K398" s="9" t="n">
-        <v>-0.065662</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="L398" s="9" t="n">
-        <v>-0.019562</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="399">
@@ -20444,34 +20444,34 @@
         <v>45931</v>
       </c>
       <c r="C399" s="10" t="n">
-        <v>0.008146</v>
+        <v>0.007</v>
       </c>
       <c r="D399" s="10" t="n">
-        <v>-0.004218</v>
+        <v>-0.007</v>
       </c>
       <c r="E399" s="10" t="n">
-        <v>0.007194</v>
+        <v>0.007</v>
       </c>
       <c r="F399" s="10" t="n">
-        <v>0.014805</v>
+        <v>0.016</v>
       </c>
       <c r="G399" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.038</v>
       </c>
       <c r="H399" s="10" t="n">
-        <v>-0.002673</v>
+        <v>-0.003</v>
       </c>
       <c r="I399" s="10" t="n">
-        <v>-0.006861</v>
+        <v>-0.007</v>
       </c>
       <c r="J399" s="10" t="n">
-        <v>0.016747</v>
+        <v>0.017</v>
       </c>
       <c r="K399" s="10" t="n">
-        <v>0.019332</v>
+        <v>0.015</v>
       </c>
       <c r="L399" s="10" t="n">
-        <v>-0.012119</v>
+        <v>-0.014</v>
       </c>
     </row>
     <row r="400">
@@ -20484,34 +20484,34 @@
         <v>45962</v>
       </c>
       <c r="C400" s="9" t="n">
-        <v>0.005953</v>
+        <v>0.006</v>
       </c>
       <c r="D400" s="9" t="n">
-        <v>-9.1e-05</v>
+        <v>-0.001</v>
       </c>
       <c r="E400" s="9" t="n">
-        <v>-6.1e-05</v>
+        <v>0</v>
       </c>
       <c r="F400" s="9" t="n">
-        <v>-0.000884</v>
+        <v>0</v>
       </c>
       <c r="G400" s="9" t="n">
-        <v>0.012471</v>
+        <v>0.016</v>
       </c>
       <c r="H400" s="9" t="n">
-        <v>0.005135</v>
+        <v>0.005</v>
       </c>
       <c r="I400" s="9" t="n">
-        <v>-0.010716</v>
+        <v>-0.01</v>
       </c>
       <c r="J400" s="9" t="n">
-        <v>0.010326</v>
+        <v>0.011</v>
       </c>
       <c r="K400" s="9" t="n">
-        <v>0.029597</v>
+        <v>0.03</v>
       </c>
       <c r="L400" s="9" t="n">
-        <v>-0.007493</v>
+        <v>-0.008</v>
       </c>
     </row>
     <row r="401">
@@ -20524,34 +20524,34 @@
         <v>45992</v>
       </c>
       <c r="C401" s="10" t="n">
-        <v>0.001167</v>
+        <v>0.002</v>
       </c>
       <c r="D401" s="10" t="n">
-        <v>0.013298</v>
+        <v>0.015</v>
       </c>
       <c r="E401" s="10" t="n">
-        <v>0.005029</v>
+        <v>0.005</v>
       </c>
       <c r="F401" s="10" t="n">
-        <v>0.003872</v>
+        <v>0.007</v>
       </c>
       <c r="G401" s="10" t="n">
-        <v>0.011943</v>
+        <v>0.012</v>
       </c>
       <c r="H401" s="10" t="n">
-        <v>-0.001648</v>
+        <v>-0.001</v>
       </c>
       <c r="I401" s="10" t="n">
-        <v>0.004242</v>
+        <v>0.005</v>
       </c>
       <c r="J401" s="10" t="n">
-        <v>0.03816</v>
+        <v>0.039</v>
       </c>
       <c r="K401" s="10" t="n">
-        <v>0.062986</v>
+        <v>0.068</v>
       </c>
       <c r="L401" s="10" t="n">
-        <v>-0.000375</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="402">
@@ -20564,34 +20564,34 @@
         <v>46023</v>
       </c>
       <c r="C402" s="9" t="n">
-        <v>-0.009527000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="D402" s="9" t="n">
-        <v>0.001362</v>
+        <v>-0.001</v>
       </c>
       <c r="E402" s="9" t="n">
-        <v>-0.010647</v>
+        <v>-0.011</v>
       </c>
       <c r="F402" s="9" t="n">
-        <v>-0.016601</v>
+        <v>-0.019</v>
       </c>
       <c r="G402" s="9" t="n">
-        <v>-0.014514</v>
+        <v>-0.011</v>
       </c>
       <c r="H402" s="9" t="n">
-        <v>-0.009401</v>
+        <v>-0.011</v>
       </c>
       <c r="I402" s="9" t="n">
-        <v>0.01057</v>
+        <v>0.01</v>
       </c>
       <c r="J402" s="9" t="n">
-        <v>0.008718</v>
+        <v>0.006</v>
       </c>
       <c r="K402" s="9" t="n">
-        <v>0.044905</v>
+        <v>0.05</v>
       </c>
       <c r="L402" s="9" t="n">
-        <v>-0.013779</v>
+        <v>-0.017</v>
       </c>
     </row>
     <row r="403">
@@ -20604,34 +20604,34 @@
         <v>46054</v>
       </c>
       <c r="C403" s="10" t="n">
-        <v>0.004961</v>
+        <v>0.004</v>
       </c>
       <c r="D403" s="10" t="n">
-        <v>-0.01101</v>
+        <v>-0.013</v>
       </c>
       <c r="E403" s="10" t="n">
-        <v>0.013648</v>
+        <v>0.006</v>
       </c>
       <c r="F403" s="10" t="n">
-        <v>-0.014735</v>
+        <v>-0.014</v>
       </c>
       <c r="G403" s="10" t="n">
-        <v>0.003412</v>
+        <v>0.003</v>
       </c>
       <c r="H403" s="10" t="n">
-        <v>0.007177</v>
+        <v>0.007</v>
       </c>
       <c r="I403" s="10" t="n">
-        <v>0.019778</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J403" s="10" t="n">
-        <v>-0.012904</v>
+        <v>-0.014</v>
       </c>
       <c r="K403" s="10" t="n">
-        <v>0.009519</v>
+        <v>0.012</v>
       </c>
       <c r="L403" s="10" t="n">
-        <v>-0.020903</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="404">
@@ -20644,34 +20644,34 @@
         <v>46082</v>
       </c>
       <c r="C404" s="9" t="n">
-        <v>-0.005572</v>
+        <v>-0.006</v>
       </c>
       <c r="D404" s="9" t="n">
-        <v>-0.012715</v>
+        <v>-0.015</v>
       </c>
       <c r="E404" s="9" t="n">
-        <v>0.006348</v>
+        <v>0.017</v>
       </c>
       <c r="F404" s="9" t="n">
-        <v>0.003971</v>
+        <v>0.003</v>
       </c>
       <c r="G404" s="9" t="n">
-        <v>-0.028244</v>
+        <v>-0.033</v>
       </c>
       <c r="H404" s="9" t="n">
-        <v>-0.001174</v>
+        <v>-0.002</v>
       </c>
       <c r="I404" s="9" t="n">
-        <v>0.054641</v>
+        <v>0.058</v>
       </c>
       <c r="J404" s="9" t="n">
-        <v>0.002199</v>
+        <v>0.003</v>
       </c>
       <c r="K404" s="9" t="n">
-        <v>-0.044944</v>
+        <v>-0.053</v>
       </c>
       <c r="L404" s="9" t="n">
-        <v>-0.013012</v>
+        <v>-0.016</v>
       </c>
     </row>
     <row r="405">
@@ -20684,34 +20684,34 @@
         <v>46113</v>
       </c>
       <c r="C405" s="10" t="n">
-        <v>0.020866</v>
+        <v>0.021</v>
       </c>
       <c r="D405" s="10" t="n">
-        <v>0.018312</v>
+        <v>0.018</v>
       </c>
       <c r="E405" s="10" t="n">
-        <v>-0.001797</v>
+        <v>-0.007</v>
       </c>
       <c r="F405" s="10" t="n">
-        <v>-0.00149</v>
+        <v>-0.003</v>
       </c>
       <c r="G405" s="10" t="n">
-        <v>0.069872</v>
+        <v>0.076</v>
       </c>
       <c r="H405" s="10" t="n">
-        <v>0.010992</v>
+        <v>0.012</v>
       </c>
       <c r="I405" s="10" t="n">
-        <v>0.034811</v>
+        <v>0.034</v>
       </c>
       <c r="J405" s="10" t="n">
-        <v>-0.00158</v>
+        <v>-0.003</v>
       </c>
       <c r="K405" s="10" t="n">
-        <v>0.08813699999999999</v>
+        <v>0.102</v>
       </c>
       <c r="L405" s="10" t="n">
-        <v>-0.002771</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="406">
@@ -20724,34 +20724,34 @@
         <v>46143</v>
       </c>
       <c r="C406" s="9" t="n">
-        <v>-0.00711</v>
+        <v>-0.008</v>
       </c>
       <c r="D406" s="9" t="n">
-        <v>0.001591</v>
+        <v>0</v>
       </c>
       <c r="E406" s="9" t="n">
-        <v>0.003397</v>
+        <v>-0.001</v>
       </c>
       <c r="F406" s="9" t="n">
-        <v>-0.003632</v>
+        <v>-0.005</v>
       </c>
       <c r="G406" s="9" t="n">
-        <v>-0.036643</v>
+        <v>-0.037</v>
       </c>
       <c r="H406" s="9" t="n">
-        <v>-0.000924</v>
+        <v>-0.001</v>
       </c>
       <c r="I406" s="9" t="n">
-        <v>0.04672</v>
+        <v>0.04</v>
       </c>
       <c r="J406" s="9" t="n">
-        <v>-0.007614</v>
+        <v>-0.008</v>
       </c>
       <c r="K406" s="9" t="n">
-        <v>-0.004984</v>
+        <v>-0.006</v>
       </c>
       <c r="L406" s="9" t="n">
-        <v>-0.0041</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="407">
@@ -20764,34 +20764,34 @@
         <v>46174</v>
       </c>
       <c r="C407" s="10" t="n">
-        <v>0.0022</v>
+        <v>0.002</v>
       </c>
       <c r="D407" s="10" t="n">
-        <v>0.007815000000000001</v>
+        <v>0.008</v>
       </c>
       <c r="E407" s="10" t="n">
-        <v>0.006232</v>
+        <v>0.006</v>
       </c>
       <c r="F407" s="10" t="n">
-        <v>0.009294</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G407" s="10" t="n">
-        <v>0.029898</v>
+        <v>0.03</v>
       </c>
       <c r="H407" s="10" t="n">
-        <v>-0.006086</v>
+        <v>-0.006</v>
       </c>
       <c r="I407" s="10" t="n">
-        <v>0.06959799999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J407" s="10" t="n">
-        <v>0.006899</v>
+        <v>0.007</v>
       </c>
       <c r="K407" s="10" t="n">
-        <v>0.042371</v>
+        <v>0.042</v>
       </c>
       <c r="L407" s="10" t="n">
-        <v>-0.011629</v>
+        <v>-0.012</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/indicadores/IMAI/IMAI_datos.xlsx
+++ b/downloads/indicadores/IMAI/IMAI_datos.xlsx
@@ -10108,7 +10108,7 @@
         <v>45597</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>103.3</v>
+        <v>101.323968</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>90.242272</v>
@@ -10133,7 +10133,7 @@
         <v>45627</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>101.4</v>
+        <v>100.10177</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>89.34519</v>
@@ -10158,7 +10158,7 @@
         <v>45658</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>100.8</v>
+        <v>100.329934</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>87.840372</v>
@@ -10183,7 +10183,7 @@
         <v>45689</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>103.2</v>
+        <v>102.088963</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>88.23526</v>
@@ -10208,7 +10208,7 @@
         <v>45717</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>102.5</v>
+        <v>101.695397</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>85.86011499999999</v>
@@ -10233,7 +10233,7 @@
         <v>45748</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>102.5</v>
+        <v>100.654217</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>87.348224</v>
@@ -10258,7 +10258,7 @@
         <v>45778</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>103.3</v>
+        <v>101.606909</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>86.6478</v>
@@ -10283,7 +10283,7 @@
         <v>45809</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>103.2</v>
+        <v>101.201605</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>85.322898</v>
@@ -10308,7 +10308,7 @@
         <v>45839</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>101.6</v>
+        <v>100.238256</v>
       </c>
       <c r="D396" s="6" t="n">
         <v>87.70510299999999</v>
@@ -10333,7 +10333,7 @@
         <v>45870</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>101.1</v>
+        <v>100.052653</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>87.990143</v>
@@ -10358,7 +10358,7 @@
         <v>45901</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>99.5</v>
+        <v>99.90134500000001</v>
       </c>
       <c r="D398" s="6" t="n">
         <v>88.643006</v>
@@ -10383,7 +10383,7 @@
         <v>45931</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>100.5</v>
+        <v>100.715175</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>89.280682</v>
@@ -10408,7 +10408,7 @@
         <v>45962</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>101.4</v>
+        <v>101.314732</v>
       </c>
       <c r="D400" s="6" t="n">
         <v>89.27523100000001</v>
@@ -10433,7 +10433,7 @@
         <v>45992</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>101.7</v>
+        <v>101.432921</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>89.72416699999999</v>
@@ -10458,7 +10458,7 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>100.3</v>
+        <v>100.466565</v>
       </c>
       <c r="D402" s="6" t="n">
         <v>88.76888</v>
@@ -10483,7 +10483,7 @@
         <v>46054</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>100.7</v>
+        <v>100.964971</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>89.98042100000001</v>
@@ -10508,7 +10508,7 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>99.90000000000001</v>
+        <v>100.402353</v>
       </c>
       <c r="D404" s="6" t="n">
         <v>90.551627</v>
@@ -10533,7 +10533,7 @@
         <v>46113</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>102.4</v>
+        <v>102.497387</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>90.388932</v>
@@ -10558,7 +10558,7 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>101.6</v>
+        <v>101.768601</v>
       </c>
       <c r="D406" s="6" t="n">
         <v>90.69598499999999</v>
@@ -10583,7 +10583,7 @@
         <v>46174</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>102</v>
+        <v>101.992466</v>
       </c>
       <c r="D407" s="7" t="n">
         <v>91.26119300000001</v>
@@ -20004,34 +20004,34 @@
         <v>45597</v>
       </c>
       <c r="C388" s="9" t="n">
-        <v>0.001</v>
+        <v>0.001801</v>
       </c>
       <c r="D388" s="9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.017317</v>
       </c>
       <c r="E388" s="9" t="n">
-        <v>0.004</v>
+        <v>0.003835</v>
       </c>
       <c r="F388" s="9" t="n">
-        <v>0.008</v>
+        <v>0.005466</v>
       </c>
       <c r="G388" s="9" t="n">
-        <v>-0.018</v>
+        <v>0.002376</v>
       </c>
       <c r="H388" s="9" t="n">
-        <v>0.007</v>
+        <v>0.00045</v>
       </c>
       <c r="I388" s="9" t="n">
-        <v>-0.045</v>
+        <v>-0.075626</v>
       </c>
       <c r="J388" s="9" t="n">
-        <v>0.029</v>
+        <v>-0.015477</v>
       </c>
       <c r="K388" s="9" t="n">
-        <v>-0.044</v>
+        <v>-0.042407</v>
       </c>
       <c r="L388" s="9" t="n">
-        <v>0.005</v>
+        <v>-0.000431</v>
       </c>
     </row>
     <row r="389">
@@ -20044,34 +20044,34 @@
         <v>45627</v>
       </c>
       <c r="C389" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.012062</v>
       </c>
       <c r="D389" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.028504</v>
       </c>
       <c r="E389" s="10" t="n">
-        <v>-0.01</v>
+        <v>-0.009941</v>
       </c>
       <c r="F389" s="10" t="n">
-        <v>-0.019</v>
+        <v>-0.023042</v>
       </c>
       <c r="G389" s="10" t="n">
-        <v>-0.021</v>
+        <v>-0.019843</v>
       </c>
       <c r="H389" s="10" t="n">
-        <v>-0.012</v>
+        <v>-0.008756</v>
       </c>
       <c r="I389" s="10" t="n">
-        <v>-0.062</v>
+        <v>-0.087746</v>
       </c>
       <c r="J389" s="10" t="n">
-        <v>0.018</v>
+        <v>-0.026871</v>
       </c>
       <c r="K389" s="10" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.061743</v>
       </c>
       <c r="L389" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.005903</v>
       </c>
     </row>
     <row r="390">
@@ -20084,34 +20084,34 @@
         <v>45658</v>
       </c>
       <c r="C390" s="9" t="n">
-        <v>-0.004</v>
+        <v>0.002279</v>
       </c>
       <c r="D390" s="9" t="n">
-        <v>-0.028</v>
+        <v>-0.031809</v>
       </c>
       <c r="E390" s="9" t="n">
-        <v>-0.018</v>
+        <v>-0.016843</v>
       </c>
       <c r="F390" s="9" t="n">
-        <v>-0.008</v>
+        <v>0.012102</v>
       </c>
       <c r="G390" s="9" t="n">
-        <v>0.001</v>
+        <v>0.002539</v>
       </c>
       <c r="H390" s="9" t="n">
-        <v>-0.003</v>
+        <v>0.004062</v>
       </c>
       <c r="I390" s="9" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.117057</v>
       </c>
       <c r="J390" s="9" t="n">
-        <v>0.01</v>
+        <v>0.021327</v>
       </c>
       <c r="K390" s="9" t="n">
-        <v>-0.064</v>
+        <v>-0.080691</v>
       </c>
       <c r="L390" s="9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.00448</v>
       </c>
     </row>
     <row r="391">
@@ -20124,34 +20124,34 @@
         <v>45689</v>
       </c>
       <c r="C391" s="10" t="n">
-        <v>0.025</v>
+        <v>0.017532</v>
       </c>
       <c r="D391" s="10" t="n">
-        <v>0.004</v>
+        <v>0.000743</v>
       </c>
       <c r="E391" s="10" t="n">
-        <v>0.008</v>
+        <v>0.004496</v>
       </c>
       <c r="F391" s="10" t="n">
-        <v>-0.004</v>
+        <v>0.006847</v>
       </c>
       <c r="G391" s="10" t="n">
-        <v>0.028</v>
+        <v>0.038584</v>
       </c>
       <c r="H391" s="10" t="n">
-        <v>0.029</v>
+        <v>0.014505</v>
       </c>
       <c r="I391" s="10" t="n">
-        <v>-0.063</v>
+        <v>-0.102963</v>
       </c>
       <c r="J391" s="10" t="n">
-        <v>-0.011</v>
+        <v>0.003246</v>
       </c>
       <c r="K391" s="10" t="n">
-        <v>0.005</v>
+        <v>0.002515</v>
       </c>
       <c r="L391" s="10" t="n">
-        <v>0.018</v>
+        <v>0.018217</v>
       </c>
     </row>
     <row r="392">
@@ -20164,34 +20164,34 @@
         <v>45717</v>
       </c>
       <c r="C392" s="9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.003855</v>
       </c>
       <c r="D392" s="9" t="n">
-        <v>-0.013</v>
+        <v>-0.009154000000000001</v>
       </c>
       <c r="E392" s="9" t="n">
-        <v>-0.027</v>
+        <v>-0.026918</v>
       </c>
       <c r="F392" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.011159</v>
       </c>
       <c r="G392" s="9" t="n">
-        <v>0.008</v>
+        <v>0.027171</v>
       </c>
       <c r="H392" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.009159</v>
       </c>
       <c r="I392" s="9" t="n">
-        <v>-0.101</v>
+        <v>-0.106163</v>
       </c>
       <c r="J392" s="9" t="n">
-        <v>-0.034</v>
+        <v>-0.018411</v>
       </c>
       <c r="K392" s="9" t="n">
-        <v>0.021</v>
+        <v>0.024595</v>
       </c>
       <c r="L392" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.003725</v>
       </c>
     </row>
     <row r="393">
@@ -20204,34 +20204,34 @@
         <v>45748</v>
       </c>
       <c r="C393" s="10" t="n">
-        <v>0.001</v>
+        <v>-0.010238</v>
       </c>
       <c r="D393" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.009716000000000001</v>
       </c>
       <c r="E393" s="10" t="n">
-        <v>0.013</v>
+        <v>0.017332</v>
       </c>
       <c r="F393" s="10" t="n">
-        <v>0.001</v>
+        <v>0.00229</v>
       </c>
       <c r="G393" s="10" t="n">
-        <v>-0.02</v>
+        <v>-0.060975</v>
       </c>
       <c r="H393" s="10" t="n">
-        <v>0.007</v>
+        <v>0.00061</v>
       </c>
       <c r="I393" s="10" t="n">
-        <v>-0.068</v>
+        <v>-0.07326199999999999</v>
       </c>
       <c r="J393" s="10" t="n">
-        <v>-0.001</v>
+        <v>0.012085</v>
       </c>
       <c r="K393" s="10" t="n">
-        <v>-0.027</v>
+        <v>-0.048826</v>
       </c>
       <c r="L393" s="10" t="n">
-        <v>0.014</v>
+        <v>0.015752</v>
       </c>
     </row>
     <row r="394">
@@ -20244,34 +20244,34 @@
         <v>45778</v>
       </c>
       <c r="C394" s="9" t="n">
-        <v>0.006</v>
+        <v>0.009464999999999999</v>
       </c>
       <c r="D394" s="9" t="n">
-        <v>-0.004</v>
+        <v>-0.002243</v>
       </c>
       <c r="E394" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.008019</v>
       </c>
       <c r="F394" s="9" t="n">
-        <v>0.004</v>
+        <v>0.002426</v>
       </c>
       <c r="G394" s="9" t="n">
-        <v>0.028</v>
+        <v>0.053515</v>
       </c>
       <c r="H394" s="9" t="n">
-        <v>0.001</v>
+        <v>0.000409</v>
       </c>
       <c r="I394" s="9" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.08178299999999999</v>
       </c>
       <c r="J394" s="9" t="n">
-        <v>-0.038</v>
+        <v>-0.02676</v>
       </c>
       <c r="K394" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.009742000000000001</v>
       </c>
       <c r="L394" s="9" t="n">
-        <v>0.014</v>
+        <v>0.015008</v>
       </c>
     </row>
     <row r="395">
@@ -20284,34 +20284,34 @@
         <v>45809</v>
       </c>
       <c r="C395" s="10" t="n">
-        <v>-0.001</v>
+        <v>-0.003989</v>
       </c>
       <c r="D395" s="10" t="n">
-        <v>-0.008</v>
+        <v>-0.008612</v>
       </c>
       <c r="E395" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.015291</v>
       </c>
       <c r="F395" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.005253</v>
       </c>
       <c r="G395" s="10" t="n">
-        <v>-0.002</v>
+        <v>-0.01689</v>
       </c>
       <c r="H395" s="10" t="n">
-        <v>0.003</v>
+        <v>0.001485</v>
       </c>
       <c r="I395" s="10" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.082473</v>
       </c>
       <c r="J395" s="10" t="n">
-        <v>-0.038</v>
+        <v>-0.028596</v>
       </c>
       <c r="K395" s="10" t="n">
-        <v>0.015</v>
+        <v>0.004225</v>
       </c>
       <c r="L395" s="10" t="n">
-        <v>0</v>
+        <v>0.00055</v>
       </c>
     </row>
     <row r="396">
@@ -20324,34 +20324,34 @@
         <v>45839</v>
       </c>
       <c r="C396" s="9" t="n">
-        <v>-0.012</v>
+        <v>-0.009519</v>
       </c>
       <c r="D396" s="9" t="n">
-        <v>-0.028</v>
+        <v>-0.024575</v>
       </c>
       <c r="E396" s="9" t="n">
-        <v>0.019</v>
+        <v>0.02792</v>
       </c>
       <c r="F396" s="9" t="n">
-        <v>-0.001</v>
+        <v>-0.000549</v>
       </c>
       <c r="G396" s="9" t="n">
-        <v>-0.012</v>
+        <v>-0.002394</v>
       </c>
       <c r="H396" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.015605</v>
       </c>
       <c r="I396" s="9" t="n">
-        <v>-0.059</v>
+        <v>-0.059472</v>
       </c>
       <c r="J396" s="9" t="n">
-        <v>-0.037</v>
+        <v>-0.026099</v>
       </c>
       <c r="K396" s="9" t="n">
-        <v>-0.041</v>
+        <v>-0.041751</v>
       </c>
       <c r="L396" s="9" t="n">
-        <v>-0.018</v>
+        <v>-0.013886</v>
       </c>
     </row>
     <row r="397">
@@ -20364,34 +20364,34 @@
         <v>45870</v>
       </c>
       <c r="C397" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.001852</v>
       </c>
       <c r="D397" s="10" t="n">
-        <v>-0.027</v>
+        <v>-0.021587</v>
       </c>
       <c r="E397" s="10" t="n">
-        <v>-0.007</v>
+        <v>0.00325</v>
       </c>
       <c r="F397" s="10" t="n">
-        <v>0.013</v>
+        <v>0.009941</v>
       </c>
       <c r="G397" s="10" t="n">
-        <v>-0.022</v>
+        <v>-0.018026</v>
       </c>
       <c r="H397" s="10" t="n">
-        <v>0.002</v>
+        <v>0.000398</v>
       </c>
       <c r="I397" s="10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.062695</v>
       </c>
       <c r="J397" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.015806</v>
       </c>
       <c r="K397" s="10" t="n">
-        <v>-0.032</v>
+        <v>-0.022674</v>
       </c>
       <c r="L397" s="10" t="n">
-        <v>-0.017</v>
+        <v>-0.014845</v>
       </c>
     </row>
     <row r="398">
@@ -20404,34 +20404,34 @@
         <v>45901</v>
       </c>
       <c r="C398" s="9" t="n">
-        <v>-0.004</v>
+        <v>-0.001512</v>
       </c>
       <c r="D398" s="9" t="n">
-        <v>-0.033</v>
+        <v>-0.029057</v>
       </c>
       <c r="E398" s="9" t="n">
-        <v>0.007</v>
+        <v>0.00742</v>
       </c>
       <c r="F398" s="9" t="n">
-        <v>0.004</v>
+        <v>0.003361</v>
       </c>
       <c r="G398" s="9" t="n">
-        <v>-0.025</v>
+        <v>-0.020885</v>
       </c>
       <c r="H398" s="9" t="n">
-        <v>0.002</v>
+        <v>0.002406</v>
       </c>
       <c r="I398" s="9" t="n">
-        <v>-0.032</v>
+        <v>-0.032038</v>
       </c>
       <c r="J398" s="9" t="n">
-        <v>-0.002</v>
+        <v>-0.001671</v>
       </c>
       <c r="K398" s="9" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.065662</v>
       </c>
       <c r="L398" s="9" t="n">
-        <v>-0.023</v>
+        <v>-0.019562</v>
       </c>
     </row>
     <row r="399">
@@ -20444,34 +20444,34 @@
         <v>45931</v>
       </c>
       <c r="C399" s="10" t="n">
-        <v>0.007</v>
+        <v>0.008146</v>
       </c>
       <c r="D399" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.004218</v>
       </c>
       <c r="E399" s="10" t="n">
-        <v>0.007</v>
+        <v>0.007194</v>
       </c>
       <c r="F399" s="10" t="n">
-        <v>0.016</v>
+        <v>0.014805</v>
       </c>
       <c r="G399" s="10" t="n">
-        <v>0.038</v>
+        <v>0.0399</v>
       </c>
       <c r="H399" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.002673</v>
       </c>
       <c r="I399" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.006861</v>
       </c>
       <c r="J399" s="10" t="n">
-        <v>0.017</v>
+        <v>0.016747</v>
       </c>
       <c r="K399" s="10" t="n">
-        <v>0.015</v>
+        <v>0.019332</v>
       </c>
       <c r="L399" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.012119</v>
       </c>
     </row>
     <row r="400">
@@ -20484,34 +20484,34 @@
         <v>45962</v>
       </c>
       <c r="C400" s="9" t="n">
-        <v>0.006</v>
+        <v>0.005953</v>
       </c>
       <c r="D400" s="9" t="n">
-        <v>-0.001</v>
+        <v>-9.1e-05</v>
       </c>
       <c r="E400" s="9" t="n">
-        <v>0</v>
+        <v>-6.1e-05</v>
       </c>
       <c r="F400" s="9" t="n">
-        <v>0</v>
+        <v>-0.000884</v>
       </c>
       <c r="G400" s="9" t="n">
-        <v>0.016</v>
+        <v>0.012471</v>
       </c>
       <c r="H400" s="9" t="n">
-        <v>0.005</v>
+        <v>0.005135</v>
       </c>
       <c r="I400" s="9" t="n">
-        <v>-0.01</v>
+        <v>-0.010716</v>
       </c>
       <c r="J400" s="9" t="n">
-        <v>0.011</v>
+        <v>0.010326</v>
       </c>
       <c r="K400" s="9" t="n">
-        <v>0.03</v>
+        <v>0.029597</v>
       </c>
       <c r="L400" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.007493</v>
       </c>
     </row>
     <row r="401">
@@ -20524,34 +20524,34 @@
         <v>45992</v>
       </c>
       <c r="C401" s="10" t="n">
-        <v>0.002</v>
+        <v>0.001167</v>
       </c>
       <c r="D401" s="10" t="n">
-        <v>0.015</v>
+        <v>0.013298</v>
       </c>
       <c r="E401" s="10" t="n">
-        <v>0.005</v>
+        <v>0.005029</v>
       </c>
       <c r="F401" s="10" t="n">
-        <v>0.007</v>
+        <v>0.003872</v>
       </c>
       <c r="G401" s="10" t="n">
-        <v>0.012</v>
+        <v>0.011943</v>
       </c>
       <c r="H401" s="10" t="n">
-        <v>-0.001</v>
+        <v>-0.001648</v>
       </c>
       <c r="I401" s="10" t="n">
-        <v>0.005</v>
+        <v>0.004242</v>
       </c>
       <c r="J401" s="10" t="n">
-        <v>0.039</v>
+        <v>0.03816</v>
       </c>
       <c r="K401" s="10" t="n">
-        <v>0.068</v>
+        <v>0.062986</v>
       </c>
       <c r="L401" s="10" t="n">
-        <v>0.001</v>
+        <v>-0.000375</v>
       </c>
     </row>
     <row r="402">
@@ -20564,34 +20564,34 @@
         <v>46023</v>
       </c>
       <c r="C402" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.009527000000000001</v>
       </c>
       <c r="D402" s="9" t="n">
-        <v>-0.001</v>
+        <v>0.001362</v>
       </c>
       <c r="E402" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.010647</v>
       </c>
       <c r="F402" s="9" t="n">
-        <v>-0.019</v>
+        <v>-0.016601</v>
       </c>
       <c r="G402" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.014514</v>
       </c>
       <c r="H402" s="9" t="n">
-        <v>-0.011</v>
+        <v>-0.009401</v>
       </c>
       <c r="I402" s="9" t="n">
-        <v>0.01</v>
+        <v>0.01057</v>
       </c>
       <c r="J402" s="9" t="n">
-        <v>0.006</v>
+        <v>0.008718</v>
       </c>
       <c r="K402" s="9" t="n">
-        <v>0.05</v>
+        <v>0.044905</v>
       </c>
       <c r="L402" s="9" t="n">
-        <v>-0.017</v>
+        <v>-0.013779</v>
       </c>
     </row>
     <row r="403">
@@ -20604,34 +20604,34 @@
         <v>46054</v>
       </c>
       <c r="C403" s="10" t="n">
-        <v>0.004</v>
+        <v>0.004961</v>
       </c>
       <c r="D403" s="10" t="n">
-        <v>-0.013</v>
+        <v>-0.01101</v>
       </c>
       <c r="E403" s="10" t="n">
-        <v>0.006</v>
+        <v>0.013648</v>
       </c>
       <c r="F403" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.014735</v>
       </c>
       <c r="G403" s="10" t="n">
-        <v>0.003</v>
+        <v>0.003412</v>
       </c>
       <c r="H403" s="10" t="n">
-        <v>0.007</v>
+        <v>0.007177</v>
       </c>
       <c r="I403" s="10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.019778</v>
       </c>
       <c r="J403" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.012904</v>
       </c>
       <c r="K403" s="10" t="n">
-        <v>0.012</v>
+        <v>0.009519</v>
       </c>
       <c r="L403" s="10" t="n">
-        <v>-0.023</v>
+        <v>-0.020903</v>
       </c>
     </row>
     <row r="404">
@@ -20644,34 +20644,34 @@
         <v>46082</v>
       </c>
       <c r="C404" s="9" t="n">
-        <v>-0.006</v>
+        <v>-0.005572</v>
       </c>
       <c r="D404" s="9" t="n">
-        <v>-0.015</v>
+        <v>-0.012715</v>
       </c>
       <c r="E404" s="9" t="n">
-        <v>0.017</v>
+        <v>0.006348</v>
       </c>
       <c r="F404" s="9" t="n">
-        <v>0.003</v>
+        <v>0.003971</v>
       </c>
       <c r="G404" s="9" t="n">
-        <v>-0.033</v>
+        <v>-0.028244</v>
       </c>
       <c r="H404" s="9" t="n">
-        <v>-0.002</v>
+        <v>-0.001174</v>
       </c>
       <c r="I404" s="9" t="n">
-        <v>0.058</v>
+        <v>0.054641</v>
       </c>
       <c r="J404" s="9" t="n">
-        <v>0.003</v>
+        <v>0.002199</v>
       </c>
       <c r="K404" s="9" t="n">
-        <v>-0.053</v>
+        <v>-0.044944</v>
       </c>
       <c r="L404" s="9" t="n">
-        <v>-0.016</v>
+        <v>-0.013012</v>
       </c>
     </row>
     <row r="405">
@@ -20684,34 +20684,34 @@
         <v>46113</v>
       </c>
       <c r="C405" s="10" t="n">
-        <v>0.021</v>
+        <v>0.020866</v>
       </c>
       <c r="D405" s="10" t="n">
-        <v>0.018</v>
+        <v>0.018312</v>
       </c>
       <c r="E405" s="10" t="n">
-        <v>-0.007</v>
+        <v>-0.001797</v>
       </c>
       <c r="F405" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.00149</v>
       </c>
       <c r="G405" s="10" t="n">
-        <v>0.076</v>
+        <v>0.069872</v>
       </c>
       <c r="H405" s="10" t="n">
-        <v>0.012</v>
+        <v>0.010992</v>
       </c>
       <c r="I405" s="10" t="n">
-        <v>0.034</v>
+        <v>0.034811</v>
       </c>
       <c r="J405" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.00158</v>
       </c>
       <c r="K405" s="10" t="n">
-        <v>0.102</v>
+        <v>0.08813699999999999</v>
       </c>
       <c r="L405" s="10" t="n">
-        <v>-0.003</v>
+        <v>-0.002771</v>
       </c>
     </row>
     <row r="406">
@@ -20724,34 +20724,34 @@
         <v>46143</v>
       </c>
       <c r="C406" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.00711</v>
       </c>
       <c r="D406" s="9" t="n">
-        <v>0</v>
+        <v>0.001591</v>
       </c>
       <c r="E406" s="9" t="n">
-        <v>-0.001</v>
+        <v>0.003397</v>
       </c>
       <c r="F406" s="9" t="n">
-        <v>-0.005</v>
+        <v>-0.003632</v>
       </c>
       <c r="G406" s="9" t="n">
-        <v>-0.037</v>
+        <v>-0.036643</v>
       </c>
       <c r="H406" s="9" t="n">
-        <v>-0.001</v>
+        <v>-0.000924</v>
       </c>
       <c r="I406" s="9" t="n">
-        <v>0.04</v>
+        <v>0.04672</v>
       </c>
       <c r="J406" s="9" t="n">
-        <v>-0.008</v>
+        <v>-0.007614</v>
       </c>
       <c r="K406" s="9" t="n">
-        <v>-0.006</v>
+        <v>-0.004984</v>
       </c>
       <c r="L406" s="9" t="n">
-        <v>-0.005</v>
+        <v>-0.0041</v>
       </c>
     </row>
     <row r="407">
@@ -20764,34 +20764,34 @@
         <v>46174</v>
       </c>
       <c r="C407" s="10" t="n">
-        <v>0.002</v>
+        <v>0.0022</v>
       </c>
       <c r="D407" s="10" t="n">
-        <v>0.008</v>
+        <v>0.007815000000000001</v>
       </c>
       <c r="E407" s="10" t="n">
-        <v>0.006</v>
+        <v>0.006232</v>
       </c>
       <c r="F407" s="10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009294</v>
       </c>
       <c r="G407" s="10" t="n">
-        <v>0.03</v>
+        <v>0.029898</v>
       </c>
       <c r="H407" s="10" t="n">
-        <v>-0.006</v>
+        <v>-0.006086</v>
       </c>
       <c r="I407" s="10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06959799999999999</v>
       </c>
       <c r="J407" s="10" t="n">
-        <v>0.007</v>
+        <v>0.006899</v>
       </c>
       <c r="K407" s="10" t="n">
-        <v>0.042</v>
+        <v>0.042371</v>
       </c>
       <c r="L407" s="10" t="n">
-        <v>-0.012</v>
+        <v>-0.011629</v>
       </c>
     </row>
   </sheetData>
